--- a/metadata/atacseq/todo/TMC - University of California San Diego focusing on female reproduction (ATACseq).xlsx
+++ b/metadata/atacseq/todo/TMC - University of California San Diego focusing on female reproduction (ATACseq).xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 4 slides, 16 reactions; PN 1000184</t>
+          <t>10x Genomics; Chromium Next GEM Single Cell Fixed RNA Sample Preparation Kit, 16 rxns; PN 1000414</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -507,7 +507,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>Parse Biosciences; Evercode WT v2 Kit, 48 rxns; PN ECW02030</t>
+          <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 4 slides, 16 reactions; PN 1000184</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 16 rxns; PN 1000263</t>
+          <t>Parse Biosciences; Evercode WT v2 Kit, 48 rxns; PN ECW02030</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -546,7 +546,7 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Human Transcriptome, 1 slides, 4 reactions; PN 1000338</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 16 rxns; PN 1000263</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 16 rxns; PN 1000268</t>
+          <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Human Transcriptome, 1 slides, 4 reactions; PN 1000338</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -570,7 +570,7 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Next GEM Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000175</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 16 rxns; PN 1000268</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -582,7 +582,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>10x Genomics; Library Construction Kit C, 16 rxns; PN 1000694</t>
+          <t>10x Genomics; Chromium Next GEM Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000175</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -594,7 +594,7 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>10x Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Mouse Transcriptome, 6.5mm, 4 rxns; PN 1000521</t>
+          <t>10x Genomics; Library Construction Kit C, 16 rxns; PN 1000694</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 3' HT Kit v3.1, 48 rxns; PN 1000348</t>
+          <t>10x Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Mouse Transcriptome, 6.5mm, 4 rxns; PN 1000521</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 3' GEM, Library &amp; Gel Bead Kit v3.1, 16 rxns; PN 1000121</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell 3' HT Kit v3.1, 48 rxns; PN 1000348</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>10x Genomics; Library Construction Kit C, 4 rxns; PN 1000689</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell 3' GEM, Library &amp; Gel Bead Kit v3.1, 16 rxns; PN 1000121</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 11 mm, 2 reactions; PN 1000522</t>
+          <t>10x Genomics; Library Construction Kit C, 4 rxns; PN 1000689</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -654,7 +654,7 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Illumina; TruSeq Stranded mRNA Library Prep (48 samples); PN 20020594</t>
+          <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 11 mm, 2 reactions; PN 1000522</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -666,7 +666,7 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>10X Genomics; Automated Library Construction Kit, 24 rxns; PN 1000428</t>
+          <t>Illumina; TruSeq Stranded mRNA Library Prep (48 samples); PN 20020594</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>New England BioLabs; NEBNext Ultra II RNA Library Prep Kit for Illumina; PN E7770</t>
+          <t>10X Genomics; Automated Library Construction Kit, 24 rxns; PN 1000428</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -690,7 +690,7 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Automated Single Cell 5' Kit v2, 24 rxns; PN 1000290</t>
+          <t>New England BioLabs; NEBNext Ultra II RNA Library Prep Kit for Illumina; PN E7770</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 1 slides, 4 reactions; PN 1000187</t>
+          <t>10X Genomics; Chromium Next GEM Automated Single Cell 5' Kit v2, 24 rxns; PN 1000290</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -714,124 +714,145 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium GEM-X Single Cell 5' Kit v3, 16 rxns; PN 1000699</t>
+          <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 1 slides, 4 reactions; PN 1000187</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000110</t>
+          <t>10x Genomics; Chromium GEM-X Single Cell 5' Kit v3, 16 rxns; PN 1000699</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>10x Genomics; Library Construction Kit, 16 rxns; PN 1000190</t>
+          <t>10x Genomics; Chromium Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000110</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Parse Biosciences; Evercode WT Mini v2 Kit, 12 rxns; PN ECW02010</t>
+          <t>10x Genomics; Library Construction Kit, 16 rxns; PN 1000190</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 48 rxns; PN 1000356</t>
+          <t>Parse Biosciences; Evercode WT Mini v2 Kit, 12 rxns; PN ECW02010</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Illumina; TruSeq Stranded mRNA Library Prep (96 samples); PN 20020595</t>
+          <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 48 rxns; PN 1000356</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 4 rxns; PN 1000265</t>
+          <t>Illumina; TruSeq Stranded mRNA Library Prep (96 samples); PN 20020595</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 4 rxn; PN 1000285</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 4 rxns; PN 1000265</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell Fixed RNA Hybridization &amp; Library Kit, 4 rxns; PN 1000415</t>
+          <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 4 rxn; PN 1000285</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>10X Genomics; Chromium Next GEM Single Cell Fixed RNA Hybridization &amp; Library Kit, 4 rxns; PN 1000415</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Single Cell 3' GEM, Library &amp; Gel Bead Kit v3, 4 rxns; PN 1000092</t>
+          <t>Custom</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Single Cell 3ʹ GEM, Library &amp; Gel Bead Kit v3, 16 rxns; PN 1000075</t>
+          <t>10X Genomics; Chromium Single Cell 3' GEM, Library &amp; Gel Bead Kit v3, 4 rxns; PN 1000092</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Single Cell 3' Library &amp; Gel Bead Kit, 4 rxns; PN 120267</t>
+          <t>10x Genomics; Chromium Single Cell 3ʹ GEM, Library &amp; Gel Bead Kit v3, 16 rxns; PN 1000075</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Mouse Transcriptome, 4 rxns; PN 1000339</t>
+          <t>10X Genomics; Chromium Single Cell 3' Library &amp; Gel Bead Kit, 4 rxns; PN 120267</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 16 rxn; PN 1000283</t>
+          <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Mouse Transcriptome, 4 rxns; PN 1000339</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 4 rxns; PN 1000269</t>
+          <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 16 rxn; PN 1000283</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 8 rxns; PN 1000374</t>
+          <t>Epigenome Technologies; Multiplex Droplet Paired-Tag 16 Reaction Kit; PN MDP16101</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
+        <is>
+          <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 4 rxns; PN 1000269</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10x Genomics; GEM-X Flex GEM &amp; Library Kit, 4 rxns; PN 1000782</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 8 rxns; PN 1000374</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
         <is>
           <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 6.5mm, 4 reactions; PN 1000520</t>
         </is>
@@ -9971,7 +9992,7 @@
       <formula1>_validation_data!$A$1:$A$3</formula1>
     </dataValidation>
     <dataValidation sqref="C248 C275" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
-      <formula1>_validation_data!$B$1:$B$37</formula1>
+      <formula1>_validation_data!$B$1:$B$40</formula1>
     </dataValidation>
     <dataValidation sqref="C249 C276" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
       <formula1>_validation_data!$C$1:$C$19</formula1>
